--- a/web/public/sample_assets_messy.xlsx
+++ b/web/public/sample_assets_messy.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>정보화담당관실</t>
+          <t>정보화팀</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>도로국</t>
+          <t>시설관리과</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
